--- a/data/trans_orig/P5709-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5709-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2007</t>
+          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>413773</t>
+          <t>410681</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>475806</t>
+          <t>472052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>477672</t>
+          <t>476480</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>550041</t>
+          <t>546018</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>911798</t>
+          <t>911927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1003686</t>
+          <t>1008880</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249114</t>
+          <t>253243</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307982</t>
+          <t>310250</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273388</t>
+          <t>273945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>335824</t>
+          <t>331537</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>542902</t>
+          <t>540178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>625785</t>
+          <t>624243</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>190845</t>
+          <t>191676</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>240103</t>
+          <t>244971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>287552</t>
+          <t>289713</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>351650</t>
+          <t>352241</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>495617</t>
+          <t>493598</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>577017</t>
+          <t>575601</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57728</t>
+          <t>56322</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92018</t>
+          <t>90308</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120866</t>
+          <t>121894</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>165904</t>
+          <t>164614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>185454</t>
+          <t>186699</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>242615</t>
+          <t>243711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12360</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32364</t>
+          <t>31530</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26998</t>
+          <t>27782</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52658</t>
+          <t>53107</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44277</t>
+          <t>43651</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75856</t>
+          <t>75816</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>988022</t>
+          <t>989228</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1068896</t>
+          <t>1071302</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>848581</t>
+          <t>847519</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>923369</t>
+          <t>926170</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1856582</t>
+          <t>1859583</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1975533</t>
+          <t>1973648</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,17%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>378563</t>
+          <t>376771</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>447457</t>
+          <t>449365</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>342230</t>
+          <t>347049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>410752</t>
+          <t>410890</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>743373</t>
+          <t>742490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>844828</t>
+          <t>837992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>172103</t>
+          <t>173333</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>222821</t>
+          <t>223259</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>213204</t>
+          <t>209602</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>267793</t>
+          <t>267368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>397558</t>
+          <t>395623</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>477187</t>
+          <t>476262</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33821</t>
+          <t>35527</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64419</t>
+          <t>62674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58215</t>
+          <t>57345</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94422</t>
+          <t>94103</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100080</t>
+          <t>99673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145758</t>
+          <t>145262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14498</t>
+          <t>14416</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,77 +1887,77 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11432</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5628</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>21289</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>18190</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>10287</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>28345</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>11432</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>5783</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>21847</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>18190</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>10259</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>28008</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>313851</t>
+          <t>311530</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>361951</t>
+          <t>360168</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>256980</t>
+          <t>257276</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>298777</t>
+          <t>300156</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>584879</t>
+          <t>583841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>646578</t>
+          <t>649517</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,26%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108904</t>
+          <t>108169</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>150320</t>
+          <t>151223</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105709</t>
+          <t>108011</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142800</t>
+          <t>144742</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>224065</t>
+          <t>224416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279088</t>
+          <t>284841</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50991</t>
+          <t>49898</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84025</t>
+          <t>82260</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39547</t>
+          <t>38005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66105</t>
+          <t>64919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>98068</t>
+          <t>97200</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>140181</t>
+          <t>141579</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24786</t>
+          <t>25104</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32870</t>
+          <t>31981</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>24759</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50268</t>
+          <t>50819</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1756447</t>
+          <t>1756013</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1863226</t>
+          <t>1875581</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1617248</t>
+          <t>1614821</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1742229</t>
+          <t>1733667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3406027</t>
+          <t>3412580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3576341</t>
+          <t>3571202</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>778006</t>
+          <t>774293</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>872461</t>
+          <t>871965</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>755706</t>
+          <t>753543</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>851586</t>
+          <t>857141</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1554904</t>
+          <t>1558852</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1691604</t>
+          <t>1694845</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>439457</t>
+          <t>433464</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>522360</t>
+          <t>513849</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>560723</t>
+          <t>560772</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>655033</t>
+          <t>654217</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1018977</t>
+          <t>1028357</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1141140</t>
+          <t>1154002</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>114706</t>
+          <t>114215</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>160627</t>
+          <t>161478</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>208296</t>
+          <t>208667</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>270106</t>
+          <t>267043</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>333155</t>
+          <t>336162</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>412663</t>
+          <t>412850</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19529</t>
+          <t>19872</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41412</t>
+          <t>41489</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38518</t>
+          <t>37309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67694</t>
+          <t>66541</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62584</t>
+          <t>62441</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99646</t>
+          <t>98743</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2012</t>
+          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>439649</t>
+          <t>440358</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>502272</t>
+          <t>504910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>567199</t>
+          <t>566560</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>641196</t>
+          <t>643680</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1027850</t>
+          <t>1027126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1127722</t>
+          <t>1127248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>236358</t>
+          <t>235362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293110</t>
+          <t>296940</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333239</t>
+          <t>334324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>403238</t>
+          <t>403283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>587343</t>
+          <t>584648</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>677748</t>
+          <t>671815</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132115</t>
+          <t>132690</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>178577</t>
+          <t>178249</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>214552</t>
+          <t>214579</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>273285</t>
+          <t>272309</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>356819</t>
+          <t>360072</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>432823</t>
+          <t>431169</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44694</t>
+          <t>43618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75581</t>
+          <t>75774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58863</t>
+          <t>59960</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95478</t>
+          <t>94033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109659</t>
+          <t>112533</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156180</t>
+          <t>158879</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29319</t>
+          <t>30113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32051</t>
+          <t>32752</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61212</t>
+          <t>59829</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48310</t>
+          <t>48368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82024</t>
+          <t>80007</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1110036</t>
+          <t>1110039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1193101</t>
+          <t>1199363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>905068</t>
+          <t>908571</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>992455</t>
+          <t>995343</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2037092</t>
+          <t>2043700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2164921</t>
+          <t>2173015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,46%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>481666</t>
+          <t>480253</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>561956</t>
+          <t>560013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>451072</t>
+          <t>446200</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525048</t>
+          <t>519955</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>954426</t>
+          <t>947496</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1068667</t>
+          <t>1064658</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>189782</t>
+          <t>189051</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>246390</t>
+          <t>250293</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>175262</t>
+          <t>175892</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>231172</t>
+          <t>232795</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>379798</t>
+          <t>386222</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>460719</t>
+          <t>464060</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43740</t>
+          <t>43898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76023</t>
+          <t>74555</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70088</t>
+          <t>71316</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110492</t>
+          <t>110897</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123426</t>
+          <t>124209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>174162</t>
+          <t>172753</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22358</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39254</t>
+          <t>38085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26608</t>
+          <t>26383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54386</t>
+          <t>53136</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>285550</t>
+          <t>284794</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>330281</t>
+          <t>330834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>266631</t>
+          <t>268258</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>312937</t>
+          <t>310266</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>564651</t>
+          <t>570768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>625809</t>
+          <t>630067</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96667</t>
+          <t>96591</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>136134</t>
+          <t>135112</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97718</t>
+          <t>99217</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137982</t>
+          <t>136449</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207432</t>
+          <t>204407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>260190</t>
+          <t>259873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23813</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51861</t>
+          <t>52423</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25330</t>
+          <t>24866</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49461</t>
+          <t>50046</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54994</t>
+          <t>55349</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>93622</t>
+          <t>92559</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>21010</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21114</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15310</t>
+          <t>14549</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36473</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1871349</t>
+          <t>1871250</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1996521</t>
+          <t>1990925</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1784349</t>
+          <t>1781270</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1906953</t>
+          <t>1909251</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3689438</t>
+          <t>3701197</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3865448</t>
+          <t>3875837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>855646</t>
+          <t>855139</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>955754</t>
+          <t>957467</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>912096</t>
+          <t>907549</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1023641</t>
+          <t>1021353</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,47 +5901,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>25,61%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>28,82%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1752</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1871807</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1789808</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1940814</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>26,92%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>25,74%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>28,89%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1871807</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1795109</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1953364</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>26,92%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>25,82%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>369803</t>
+          <t>368414</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>452853</t>
+          <t>448563</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>440132</t>
+          <t>440874</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>521986</t>
+          <t>525719</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>833517</t>
+          <t>827171</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>948997</t>
+          <t>950696</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>108742</t>
+          <t>106536</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>152543</t>
+          <t>150569</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>151369</t>
+          <t>150442</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203941</t>
+          <t>204892</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>270373</t>
+          <t>270518</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>340435</t>
+          <t>342920</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>25427</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>51046</t>
+          <t>52737</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54657</t>
+          <t>56025</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89476</t>
+          <t>91172</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90575</t>
+          <t>88947</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>131283</t>
+          <t>132838</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2016</t>
+          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2016 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>297978</t>
+          <t>295268</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>350231</t>
+          <t>348533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>361140</t>
+          <t>361719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>428124</t>
+          <t>424789</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>676178</t>
+          <t>674968</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>762836</t>
+          <t>760455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215914</t>
+          <t>216220</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268626</t>
+          <t>267329</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263721</t>
+          <t>266701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>326547</t>
+          <t>326309</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>497073</t>
+          <t>495538</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577563</t>
+          <t>576544</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107623</t>
+          <t>110682</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149068</t>
+          <t>151272</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>171235</t>
+          <t>170945</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>225831</t>
+          <t>225104</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>287660</t>
+          <t>292959</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>356630</t>
+          <t>357860</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36999</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63105</t>
+          <t>63763</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60428</t>
+          <t>60888</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97614</t>
+          <t>97749</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106493</t>
+          <t>107242</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149393</t>
+          <t>151711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>19516</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>18784</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42446</t>
+          <t>41216</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28089</t>
+          <t>27876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54845</t>
+          <t>54663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>907609</t>
+          <t>907661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>999618</t>
+          <t>1000053</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>898856</t>
+          <t>900542</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>985012</t>
+          <t>988725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1826031</t>
+          <t>1826655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1959982</t>
+          <t>1961266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,4%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>676007</t>
+          <t>676876</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>766759</t>
+          <t>763978</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>620235</t>
+          <t>619708</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>709623</t>
+          <t>708073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1318950</t>
+          <t>1318384</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1447199</t>
+          <t>1443025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>271818</t>
+          <t>272264</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>335927</t>
+          <t>339263</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>264573</t>
+          <t>266360</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>334889</t>
+          <t>333460</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>554186</t>
+          <t>556404</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>652372</t>
+          <t>650504</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56279</t>
+          <t>55652</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91544</t>
+          <t>89639</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51814</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82052</t>
+          <t>83916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112407</t>
+          <t>115579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159591</t>
+          <t>162598</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14361</t>
+          <t>15484</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34733</t>
+          <t>35874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20838</t>
+          <t>20447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>24278</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50582</t>
+          <t>51093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>270926</t>
+          <t>272436</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>319040</t>
+          <t>320234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>288281</t>
+          <t>287840</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>334603</t>
+          <t>335065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>574521</t>
+          <t>578512</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>643376</t>
+          <t>646198</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>59,11%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157729</t>
+          <t>157776</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204601</t>
+          <t>201622</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149514</t>
+          <t>152343</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195549</t>
+          <t>197511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>320789</t>
+          <t>321312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>384981</t>
+          <t>383993</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51393</t>
+          <t>49487</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84049</t>
+          <t>81893</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36379</t>
+          <t>35736</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62224</t>
+          <t>61494</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>94894</t>
+          <t>92979</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>137301</t>
+          <t>134505</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18418</t>
+          <t>19830</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22723</t>
+          <t>23097</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>11250</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1513224</t>
+          <t>1513545</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1626890</t>
+          <t>1630909</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1590173</t>
+          <t>1591388</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1710491</t>
+          <t>1706370</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3126305</t>
+          <t>3136296</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3303105</t>
+          <t>3312498</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1083220</t>
+          <t>1083066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1200248</t>
+          <t>1195014</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1070170</t>
+          <t>1074202</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1187905</t>
+          <t>1187616</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2193379</t>
+          <t>2182960</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2352244</t>
+          <t>2351251</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>458817</t>
+          <t>459907</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>540476</t>
+          <t>543834</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>503945</t>
+          <t>500813</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>591245</t>
+          <t>586189</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>980621</t>
+          <t>979871</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1102569</t>
+          <t>1100010</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>105218</t>
+          <t>105930</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>147878</t>
+          <t>149332</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128433</t>
+          <t>127400</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>178638</t>
+          <t>178283</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>245204</t>
+          <t>247288</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>314482</t>
+          <t>315002</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25182</t>
+          <t>24813</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49286</t>
+          <t>48984</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29424</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59285</t>
+          <t>58812</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>61278</t>
+          <t>60482</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>98373</t>
+          <t>97377</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2023</t>
+          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>211342</t>
+          <t>209242</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>252634</t>
+          <t>251121</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>285597</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>325739</t>
+          <t>327941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>507387</t>
+          <t>507135</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>567497</t>
+          <t>566017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118167</t>
+          <t>116453</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>153645</t>
+          <t>154059</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>188566</t>
+          <t>188025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>227443</t>
+          <t>230228</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>312999</t>
+          <t>315518</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>368415</t>
+          <t>371256</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69831</t>
+          <t>69171</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100206</t>
+          <t>100202</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>123850</t>
+          <t>120134</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>153530</t>
+          <t>152353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>200695</t>
+          <t>201947</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>244392</t>
+          <t>246490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32705</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54085</t>
+          <t>54055</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55814</t>
+          <t>56400</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77299</t>
+          <t>78902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94334</t>
+          <t>95159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124599</t>
+          <t>126870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11484</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26867</t>
+          <t>27574</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26931</t>
+          <t>27789</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43045</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42525</t>
+          <t>42332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64993</t>
+          <t>65095</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1245058</t>
+          <t>1238978</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1642728</t>
+          <t>1602187</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>796216</t>
+          <t>852757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1262239</t>
+          <t>1264037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2169988</t>
+          <t>2182847</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2797455</t>
+          <t>2801292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,92%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>434429</t>
+          <t>463608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>716042</t>
+          <t>716653</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>466726</t>
+          <t>445958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>719009</t>
+          <t>707018</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1004045</t>
+          <t>1007771</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1392487</t>
+          <t>1401659</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>153454</t>
+          <t>152259</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>257603</t>
+          <t>255906</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>146432</t>
+          <t>147736</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>233899</t>
+          <t>233674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>328904</t>
+          <t>337227</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>473258</t>
+          <t>473292</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40093</t>
+          <t>40406</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76616</t>
+          <t>77529</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63243</t>
+          <t>64332</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>843006</t>
+          <t>714853</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118488</t>
+          <t>118161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>969032</t>
+          <t>1041715</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14128</t>
+          <t>13480</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33353</t>
+          <t>33005</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19136</t>
+          <t>19257</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44470</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36673</t>
+          <t>39914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68062</t>
+          <t>70018</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>373995</t>
+          <t>378111</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>427202</t>
+          <t>429771</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>433752</t>
+          <t>435294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>474136</t>
+          <t>476061</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>825089</t>
+          <t>824750</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>889081</t>
+          <t>891595</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159177</t>
+          <t>157821</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207025</t>
+          <t>205322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135029</t>
+          <t>130884</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170085</t>
+          <t>167888</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>303577</t>
+          <t>300132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>365023</t>
+          <t>365324</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29321</t>
+          <t>30143</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53603</t>
+          <t>54998</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27134</t>
+          <t>27704</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50699</t>
+          <t>48934</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62388</t>
+          <t>61470</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>94656</t>
+          <t>95367</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30960</t>
+          <t>33400</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8640</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23763</t>
+          <t>22287</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47303</t>
+          <t>45839</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1870411</t>
+          <t>1870434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2301496</t>
+          <t>2327653</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1508401</t>
+          <t>1508871</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2026657</t>
+          <t>2018015</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3551412</t>
+          <t>3547671</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4208718</t>
+          <t>4181695</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>58,97%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>732503</t>
+          <t>732128</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1030686</t>
+          <t>1026834</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>818552</t>
+          <t>792854</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1067483</t>
+          <t>1067927</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1683384</t>
+          <t>1669614</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2066290</t>
+          <t>2066647</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>266503</t>
+          <t>262626</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>385788</t>
+          <t>385494</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>308780</t>
+          <t>307018</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>413725</t>
+          <t>415481</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>618547</t>
+          <t>627624</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>782901</t>
+          <t>778763</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93559</t>
+          <t>93138</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>147385</t>
+          <t>145711</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>143461</t>
+          <t>143683</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>970422</t>
+          <t>1093352</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>260994</t>
+          <t>259121</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1296891</t>
+          <t>1161204</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32895</t>
+          <t>30950</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59670</t>
+          <t>57686</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53542</t>
+          <t>53741</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84602</t>
+          <t>84231</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>93386</t>
+          <t>91101</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>134842</t>
+          <t>131821</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5709-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5709-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>410681</t>
+          <t>412680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>472052</t>
+          <t>473675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>476480</t>
+          <t>477218</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>546018</t>
+          <t>546964</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>911927</t>
+          <t>910984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1008880</t>
+          <t>1004408</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253243</t>
+          <t>251050</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310250</t>
+          <t>307696</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273945</t>
+          <t>274972</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>331537</t>
+          <t>332675</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540178</t>
+          <t>543810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>624243</t>
+          <t>621778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>191676</t>
+          <t>192723</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>244971</t>
+          <t>243954</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289713</t>
+          <t>290903</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>352241</t>
+          <t>353154</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>493598</t>
+          <t>495289</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>575601</t>
+          <t>577569</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56322</t>
+          <t>56460</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90308</t>
+          <t>90189</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121894</t>
+          <t>119569</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>164614</t>
+          <t>167393</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>186699</t>
+          <t>186797</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>243711</t>
+          <t>243254</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31530</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27782</t>
+          <t>27044</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53107</t>
+          <t>53100</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43651</t>
+          <t>44628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75816</t>
+          <t>76146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>989228</t>
+          <t>988804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1071302</t>
+          <t>1074644</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>847519</t>
+          <t>845300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>926170</t>
+          <t>921700</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1859583</t>
+          <t>1860917</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1973648</t>
+          <t>1967935</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>376771</t>
+          <t>376335</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>449365</t>
+          <t>449023</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>347049</t>
+          <t>343992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>410890</t>
+          <t>412377</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>742490</t>
+          <t>743470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>837992</t>
+          <t>842576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>173333</t>
+          <t>169552</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>223259</t>
+          <t>221744</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>209602</t>
+          <t>211317</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>267368</t>
+          <t>270418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>395623</t>
+          <t>399030</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>476262</t>
+          <t>476306</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35527</t>
+          <t>35956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62674</t>
+          <t>64025</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57345</t>
+          <t>58389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94103</t>
+          <t>93685</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99673</t>
+          <t>101506</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145262</t>
+          <t>145948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5628</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21289</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>29486</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>311530</t>
+          <t>311344</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>360168</t>
+          <t>359156</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>257276</t>
+          <t>257357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>300156</t>
+          <t>300899</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>583841</t>
+          <t>583011</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>649517</t>
+          <t>649828</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,29%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108169</t>
+          <t>110313</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151223</t>
+          <t>153674</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108011</t>
+          <t>105126</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>144742</t>
+          <t>142753</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>224416</t>
+          <t>227146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>284841</t>
+          <t>284814</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49898</t>
+          <t>51715</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>82260</t>
+          <t>83386</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38005</t>
+          <t>38337</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64919</t>
+          <t>66402</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>97200</t>
+          <t>95925</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>141579</t>
+          <t>137952</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25104</t>
+          <t>24121</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31981</t>
+          <t>34223</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24759</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50819</t>
+          <t>50977</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1756013</t>
+          <t>1756269</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1875581</t>
+          <t>1868719</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1614821</t>
+          <t>1620023</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1733667</t>
+          <t>1735806</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3412580</t>
+          <t>3407300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3571202</t>
+          <t>3570682</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>774293</t>
+          <t>769933</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>871965</t>
+          <t>873622</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>753543</t>
+          <t>758354</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>857141</t>
+          <t>854940</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1558852</t>
+          <t>1555627</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1694845</t>
+          <t>1697107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>433464</t>
+          <t>441236</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>513849</t>
+          <t>524055</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>560772</t>
+          <t>560306</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>654217</t>
+          <t>652671</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1028357</t>
+          <t>1028049</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1154002</t>
+          <t>1151229</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>114215</t>
+          <t>112903</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>161478</t>
+          <t>162607</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>208667</t>
+          <t>210488</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>267043</t>
+          <t>271583</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>336162</t>
+          <t>334531</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>412850</t>
+          <t>414083</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19872</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41489</t>
+          <t>41988</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37309</t>
+          <t>35765</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66541</t>
+          <t>64979</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62441</t>
+          <t>61099</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>98743</t>
+          <t>98850</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>440358</t>
+          <t>441382</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>504910</t>
+          <t>506090</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>566560</t>
+          <t>568374</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>643680</t>
+          <t>644199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1027126</t>
+          <t>1028233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1127248</t>
+          <t>1128527</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,06%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>235362</t>
+          <t>237627</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>296940</t>
+          <t>293725</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>334324</t>
+          <t>331883</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>403283</t>
+          <t>399055</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>584648</t>
+          <t>589688</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>671815</t>
+          <t>677450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132690</t>
+          <t>131181</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>178249</t>
+          <t>179150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>214579</t>
+          <t>212845</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>272309</t>
+          <t>271023</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>360072</t>
+          <t>359497</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>431169</t>
+          <t>433205</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43618</t>
+          <t>44898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75774</t>
+          <t>76131</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59960</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94033</t>
+          <t>94125</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112533</t>
+          <t>112903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>158879</t>
+          <t>159309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30113</t>
+          <t>29366</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32752</t>
+          <t>32598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59829</t>
+          <t>60837</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48368</t>
+          <t>48869</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80007</t>
+          <t>82979</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1110039</t>
+          <t>1102375</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1199363</t>
+          <t>1193180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>908571</t>
+          <t>910158</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>995343</t>
+          <t>995700</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2043700</t>
+          <t>2040408</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2173015</t>
+          <t>2164328</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,22%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>480253</t>
+          <t>483215</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>560013</t>
+          <t>561910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>446200</t>
+          <t>444741</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>519955</t>
+          <t>521539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>947496</t>
+          <t>951237</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1064658</t>
+          <t>1060240</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>189051</t>
+          <t>188598</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>250293</t>
+          <t>246715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>175892</t>
+          <t>176056</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>232795</t>
+          <t>234029</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>386222</t>
+          <t>386141</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>464060</t>
+          <t>462586</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43898</t>
+          <t>45939</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74555</t>
+          <t>76886</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71316</t>
+          <t>69936</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110897</t>
+          <t>109122</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124209</t>
+          <t>122355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172753</t>
+          <t>171183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6140</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22358</t>
+          <t>21890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15794</t>
+          <t>15788</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38085</t>
+          <t>38819</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26383</t>
+          <t>26435</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53136</t>
+          <t>54472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>284794</t>
+          <t>283225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>330834</t>
+          <t>329067</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>268258</t>
+          <t>266367</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>310266</t>
+          <t>309141</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>570768</t>
+          <t>566537</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>630067</t>
+          <t>630093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,43%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96591</t>
+          <t>96757</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135112</t>
+          <t>137661</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99217</t>
+          <t>97441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136449</t>
+          <t>137979</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>204407</t>
+          <t>205141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>259873</t>
+          <t>262367</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25400</t>
+          <t>25062</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52423</t>
+          <t>52071</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24866</t>
+          <t>24321</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50046</t>
+          <t>50039</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55349</t>
+          <t>54325</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92559</t>
+          <t>90677</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21010</t>
+          <t>20159</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20186</t>
+          <t>20214</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14549</t>
+          <t>14235</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1871250</t>
+          <t>1870062</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1990925</t>
+          <t>1991261</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1781270</t>
+          <t>1784139</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1909251</t>
+          <t>1906768</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3701197</t>
+          <t>3692378</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3875837</t>
+          <t>3863070</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,57%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>855139</t>
+          <t>849366</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>957467</t>
+          <t>959046</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>907549</t>
+          <t>914888</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1021353</t>
+          <t>1025683</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1789808</t>
+          <t>1799816</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1940814</t>
+          <t>1951691</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>368414</t>
+          <t>370291</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>448563</t>
+          <t>450287</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>440874</t>
+          <t>440850</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>525719</t>
+          <t>521845</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>827171</t>
+          <t>837729</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>950696</t>
+          <t>946889</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>106536</t>
+          <t>106257</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>150569</t>
+          <t>155365</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>150442</t>
+          <t>150952</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>204892</t>
+          <t>203255</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>270518</t>
+          <t>271229</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>342920</t>
+          <t>342628</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25427</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>52737</t>
+          <t>52288</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56025</t>
+          <t>54747</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91172</t>
+          <t>90505</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>88947</t>
+          <t>88688</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>132838</t>
+          <t>132892</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>295268</t>
+          <t>297867</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>348533</t>
+          <t>350546</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>361719</t>
+          <t>362688</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>424789</t>
+          <t>426542</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>674968</t>
+          <t>675347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>760455</t>
+          <t>756761</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>216220</t>
+          <t>217051</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267329</t>
+          <t>267570</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266701</t>
+          <t>265955</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>326309</t>
+          <t>323875</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>495538</t>
+          <t>497417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>576544</t>
+          <t>574295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>110682</t>
+          <t>106995</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>151272</t>
+          <t>147652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>170945</t>
+          <t>169373</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>225104</t>
+          <t>225276</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>292959</t>
+          <t>289479</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>357860</t>
+          <t>357468</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>37751</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63763</t>
+          <t>64122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60888</t>
+          <t>60230</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97749</t>
+          <t>96075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,47 +7040,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,7%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>127674</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>107379</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>151595</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>6,15%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>127674</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>107242</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>151711</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>19681</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18784</t>
+          <t>19286</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41216</t>
+          <t>41202</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>28256</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54663</t>
+          <t>54703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>907661</t>
+          <t>904902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1000053</t>
+          <t>998623</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>900542</t>
+          <t>896078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>988725</t>
+          <t>992834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1826655</t>
+          <t>1831545</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1961266</t>
+          <t>1958882</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>676876</t>
+          <t>673635</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>763978</t>
+          <t>765131</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>619708</t>
+          <t>618299</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>708073</t>
+          <t>706538</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1318384</t>
+          <t>1323578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1443025</t>
+          <t>1442502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>272264</t>
+          <t>272302</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>339263</t>
+          <t>336505</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>266360</t>
+          <t>264648</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>333460</t>
+          <t>332397</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>556404</t>
+          <t>558623</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>650504</t>
+          <t>651022</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55652</t>
+          <t>55204</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89639</t>
+          <t>90417</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50423</t>
+          <t>51739</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83916</t>
+          <t>82580</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115579</t>
+          <t>115740</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162598</t>
+          <t>164635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>15271</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>36739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20447</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24278</t>
+          <t>25597</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51093</t>
+          <t>49476</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>272436</t>
+          <t>272778</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>320234</t>
+          <t>319598</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>287840</t>
+          <t>286757</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>335065</t>
+          <t>334542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>578512</t>
+          <t>576765</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>646198</t>
+          <t>644799</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,98%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157776</t>
+          <t>155953</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201622</t>
+          <t>203385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>152343</t>
+          <t>150254</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197511</t>
+          <t>196739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>321312</t>
+          <t>320431</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383993</t>
+          <t>385075</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49487</t>
+          <t>51364</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81893</t>
+          <t>84619</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35736</t>
+          <t>37782</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61494</t>
+          <t>64408</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>92979</t>
+          <t>93427</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>134505</t>
+          <t>137836</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19830</t>
+          <t>18831</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>22806</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1513545</t>
+          <t>1511422</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1630909</t>
+          <t>1633606</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1591388</t>
+          <t>1581353</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1706370</t>
+          <t>1704324</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3136296</t>
+          <t>3135909</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3312498</t>
+          <t>3296302</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,84%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1083066</t>
+          <t>1085639</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1195014</t>
+          <t>1199564</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,47 +8825,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>32,2%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>35,58%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1130763</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>1073670</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1183473</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>32,13%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>35,45%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1130763</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>1074202</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1187616</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>32,13%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2182960</t>
+          <t>2195966</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2351251</t>
+          <t>2360100</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>459907</t>
+          <t>456174</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>543834</t>
+          <t>538512</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>500813</t>
+          <t>497086</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>586189</t>
+          <t>587877</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>979871</t>
+          <t>985589</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1100010</t>
+          <t>1105980</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>105930</t>
+          <t>104964</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>149332</t>
+          <t>147981</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>127400</t>
+          <t>131593</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>178283</t>
+          <t>180291</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>247288</t>
+          <t>247873</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>315002</t>
+          <t>312770</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24813</t>
+          <t>25621</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>50050</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30165</t>
+          <t>30335</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58812</t>
+          <t>57262</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>60482</t>
+          <t>61215</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>97377</t>
+          <t>99419</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>230065</t>
+          <t>256641</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>209242</t>
+          <t>235011</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>251121</t>
+          <t>282124</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>305354</t>
+          <t>326302</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>285597</t>
+          <t>305472</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>327941</t>
+          <t>347798</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>535419</t>
+          <t>582942</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>507135</t>
+          <t>551829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>566017</t>
+          <t>615872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,3%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>135031</t>
+          <t>147588</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116453</t>
+          <t>127181</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154059</t>
+          <t>168071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>206553</t>
+          <t>227675</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>188025</t>
+          <t>208645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>230228</t>
+          <t>247866</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>341585</t>
+          <t>375263</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>315518</t>
+          <t>346878</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>371256</t>
+          <t>405532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -9831,67 +9831,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>84293</t>
+          <t>97146</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69171</t>
+          <t>80862</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100202</t>
+          <t>116306</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>16,94%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>14,1%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>150006</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>134902</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>168749</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>18,37%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>16,52%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,64%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>137995</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>120134</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>152353</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>18,39%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>16,01%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>222287</t>
+          <t>247152</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>201947</t>
+          <t>224389</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>246490</t>
+          <t>272547</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42593</t>
+          <t>53011</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>41668</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54055</t>
+          <t>71022</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,22 +9979,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66117</t>
+          <t>73038</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56400</t>
+          <t>61299</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78902</t>
+          <t>86261</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>108710</t>
+          <t>126048</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95159</t>
+          <t>108248</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126870</t>
+          <t>146824</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18221</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27574</t>
+          <t>29158</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,22 +10092,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>34522</t>
+          <t>39679</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27789</t>
+          <t>30236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>49860</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>52743</t>
+          <t>58900</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42332</t>
+          <t>46961</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65095</t>
+          <t>71604</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>510203</t>
+          <t>573606</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>510203</t>
+          <t>573606</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>510203</t>
+          <t>573606</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>750541</t>
+          <t>816700</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>750541</t>
+          <t>816700</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>750541</t>
+          <t>816700</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1260744</t>
+          <t>1390306</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1260744</t>
+          <t>1390306</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1260744</t>
+          <t>1390306</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1371483</t>
+          <t>1201760</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1238978</t>
+          <t>1149367</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1602187</t>
+          <t>1250381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1116708</t>
+          <t>1127495</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>852757</t>
+          <t>1082616</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1264037</t>
+          <t>1171328</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2488192</t>
+          <t>2329256</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2182847</t>
+          <t>2270080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2801292</t>
+          <t>2401379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>621174</t>
+          <t>694122</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>463608</t>
+          <t>644528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>716653</t>
+          <t>744669</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>623632</t>
+          <t>705450</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>445958</t>
+          <t>667309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707018</t>
+          <t>744714</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1244806</t>
+          <t>1399572</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1007771</t>
+          <t>1332486</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1401659</t>
+          <t>1458853</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>215849</t>
+          <t>239088</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>152259</t>
+          <t>209405</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>255906</t>
+          <t>276069</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>198007</t>
+          <t>225788</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>147736</t>
+          <t>201428</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>233674</t>
+          <t>251983</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>413856</t>
+          <t>464877</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>337227</t>
+          <t>425940</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>473292</t>
+          <t>507880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58618</t>
+          <t>67692</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40406</t>
+          <t>53596</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77529</t>
+          <t>87520</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>267023</t>
+          <t>72870</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64332</t>
+          <t>59482</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>714853</t>
+          <t>88761</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>325641</t>
+          <t>140562</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118161</t>
+          <t>120135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1041715</t>
+          <t>163455</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>27171</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33005</t>
+          <t>39853</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>36622</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19257</t>
+          <t>26291</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>50729</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>51806</t>
+          <t>63792</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39914</t>
+          <t>49075</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70018</t>
+          <t>82305</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2289592</t>
+          <t>2229833</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2289592</t>
+          <t>2229833</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2289592</t>
+          <t>2229833</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2234709</t>
+          <t>2168225</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2234709</t>
+          <t>2168225</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2234709</t>
+          <t>2168225</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4524301</t>
+          <t>4398059</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4524301</t>
+          <t>4398059</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4524301</t>
+          <t>4398059</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>401804</t>
+          <t>437379</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>378111</t>
+          <t>407258</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>429771</t>
+          <t>461885</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>454727</t>
+          <t>501879</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>435294</t>
+          <t>480731</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>476061</t>
+          <t>524811</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>856531</t>
+          <t>939259</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>824750</t>
+          <t>903524</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>891595</t>
+          <t>971135</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>67,17%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>180694</t>
+          <t>200358</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157821</t>
+          <t>177552</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205322</t>
+          <t>225889</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>151223</t>
+          <t>171545</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130884</t>
+          <t>154275</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167888</t>
+          <t>193514</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>331917</t>
+          <t>371903</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300132</t>
+          <t>341265</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>365324</t>
+          <t>405180</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40563</t>
+          <t>45825</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30143</t>
+          <t>34449</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54998</t>
+          <t>61778</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,22 +11230,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37057</t>
+          <t>41081</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27704</t>
+          <t>30813</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48934</t>
+          <t>52405</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>77620</t>
+          <t>86906</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>61470</t>
+          <t>71109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95367</t>
+          <t>108307</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>21992</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33400</t>
+          <t>36681</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>15903</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8793</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20829</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>32709</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22287</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45839</t>
+          <t>51901</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14632</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>645940</t>
+          <t>710852</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>645940</t>
+          <t>710852</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>645940</t>
+          <t>710852</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1306403</t>
+          <t>1445730</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1306403</t>
+          <t>1445730</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1306403</t>
+          <t>1445730</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2003352</t>
+          <t>1895780</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1870434</t>
+          <t>1832274</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2327653</t>
+          <t>1961833</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1876790</t>
+          <t>1955677</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1508871</t>
+          <t>1903382</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2018015</t>
+          <t>2007246</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3880142</t>
+          <t>3851457</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3547671</t>
+          <t>3766430</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4181695</t>
+          <t>3935548</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>936899</t>
+          <t>1042068</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>732128</t>
+          <t>979041</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1026834</t>
+          <t>1098732</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>981408</t>
+          <t>1104670</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>792854</t>
+          <t>1057223</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1067927</t>
+          <t>1150271</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1918307</t>
+          <t>2146738</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1669614</t>
+          <t>2076920</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2066647</t>
+          <t>2228870</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>340705</t>
+          <t>382059</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>262626</t>
+          <t>343665</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>385494</t>
+          <t>420570</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>373059</t>
+          <t>416875</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>307018</t>
+          <t>387205</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>415481</t>
+          <t>449966</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>713764</t>
+          <t>798935</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>627624</t>
+          <t>748199</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>778763</t>
+          <t>846932</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>120306</t>
+          <t>142694</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93138</t>
+          <t>120963</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>145711</t>
+          <t>170793</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>346755</t>
+          <t>161811</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>143683</t>
+          <t>143806</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1093352</t>
+          <t>183676</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>467061</t>
+          <t>304505</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>259121</t>
+          <t>272721</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1161204</t>
+          <t>335129</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>44472</t>
+          <t>51690</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30950</t>
+          <t>39648</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57686</t>
+          <t>66145</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>67702</t>
+          <t>80769</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53741</t>
+          <t>66424</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84231</t>
+          <t>98500</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>112174</t>
+          <t>132459</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>91101</t>
+          <t>112936</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>131821</t>
+          <t>155662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3445735</t>
+          <t>3514291</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3445735</t>
+          <t>3514291</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3445735</t>
+          <t>3514291</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3645713</t>
+          <t>3719803</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3645713</t>
+          <t>3719803</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3645713</t>
+          <t>3719803</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7091448</t>
+          <t>7234094</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7091448</t>
+          <t>7234094</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7091448</t>
+          <t>7234094</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
